--- a/AAII_Financials/Quarterly/HAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAO_QTR_FIN.xlsx
@@ -3255,10 +3255,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="E59" s="3">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="F59" s="3">
         <v>1600</v>
